--- a/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>1g=10⁻³kg,1cm³=10⁻⁶m³,相除×1000</t>
+          <t>單位換算：1 g＝10⁻³ kg、1 cm³＝10⁻⁶ m³，兩者相除等於乘以1000，所以 1 g/cm³ 就是 1000 kg/m³</t>
         </is>
       </c>
     </row>
